--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I, II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I, II</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II, I</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E320"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,49 +458,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>098036</t>
+          <t>005093</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MARUDO</t>
+          <t>ROCCA D'ARAZZO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>005093</t>
+          <t>034020</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ROCCA D'ARAZZO</t>
+          <t>MEDESANO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>006082</t>
+          <t>005089</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GIAROLE</t>
+          <t>REFRANCORE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MEDESANO</t>
+          <t>SALA BAGANZA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,88 +566,88 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>015139</t>
+          <t>034036</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MEDIGLIA</t>
+          <t>SORAGNA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>098009</t>
+          <t>006163</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CASALMAIOCCO</t>
+          <t>SOLERO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>015055</t>
+          <t>033040</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CASARILE</t>
+          <t>SAN GIORGIO PIACENTINO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>015058</t>
+          <t>098049</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,51 +657,51 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CASOREZZO</t>
+          <t>SAN ROCCO AL PORTO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>098012</t>
+          <t>033035</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CASELLE LURANI</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>005089</t>
+          <t>005099</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>REFRANCORE</t>
+          <t>SAN MARTINO ALFIERI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>006061</t>
+          <t>006129</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CONZANO</t>
+          <t>PIETRA MARAZZI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>034031</t>
+          <t>033037</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -765,66 +765,66 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SALA BAGANZA</t>
+          <t>PONTENURE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>015188</t>
+          <t>005076</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ROSATE</t>
+          <t>MONTEGROSSO D'ASTI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>034036</t>
+          <t>006141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SORAGNA</t>
+          <t>QUARGNENTO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,34 +836,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>006163</t>
+          <t>033032</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SOLERO</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>005103</t>
+          <t>006122</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -873,78 +873,78 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SCURZOLENGO</t>
+          <t>OVIGLIO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>015204</t>
+          <t>005050</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEDRIANO</t>
+          <t>COSTIGLIOLE D'ASTI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>098051</t>
+          <t>005048</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SANTO STEFANO LODIGIANO</t>
+          <t>CORTIGLIONE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>003141</t>
+          <t>005034</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -954,120 +954,120 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SOZZAGO</t>
+          <t>CELLE ENOMONDO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>005115</t>
+          <t>034013</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VIARIGI</t>
+          <t>FELINO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>098054</t>
+          <t>006068</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SOMAGLIA</t>
+          <t>FELIZZANO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>033040</t>
+          <t>005022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN GIORGIO PIACENTINO</t>
+          <t>CASTAGNOLE DELLE LANZE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>006153</t>
+          <t>098011</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN GIORGIO MONFERRATO</t>
+          <t>CASELLE LANDI</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,49 +1079,49 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>098060</t>
+          <t>005006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VILLANOVA DEL SILLARO</t>
+          <t>AZZANO D'ASTI</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>098049</t>
+          <t>005003</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN ROCCO AL PORTO</t>
+          <t>ANTIGNANO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,34 +1133,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>018160</t>
+          <t>005066</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TORREVECCHIA PIA</t>
+          <t>MOMBERCELLI</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>033035</t>
+          <t>034025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>NOCETO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,34 +1187,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>015226</t>
+          <t>006105</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TURBIGO</t>
+          <t>MONTECASTELLO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>006177</t>
+          <t>005096</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1224,51 +1224,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VALENZA</t>
+          <t>ROCCHETTA TANARO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>098046</t>
+          <t>005058</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SALERANO SUL LAMBRO</t>
+          <t>INCISA SCAPACCINO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>006185</t>
+          <t>005008</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1278,39 +1278,39 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VILLANOVA MONFERRATO</t>
+          <t>BELVEGLIO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>005099</t>
+          <t>033008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN MARTINO ALFIERI</t>
+          <t>CALENDASCO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,292 +1322,292 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>015229</t>
+          <t>033002</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VANZAGO</t>
+          <t>ALSENO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>015176</t>
+          <t>033007</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>POGLIANO MILANESE</t>
+          <t>CADEO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>098047</t>
+          <t>034014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN FIORANO</t>
+          <t>FIDENZA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>015179</t>
+          <t>034017</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PREGNANA MILANESE</t>
+          <t>FORNOVO DI TARO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>006149</t>
+          <t>033018</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ROSIGNANO MONFERRATO</t>
+          <t>CORTEMAGGIORE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>015192</t>
+          <t>005028</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAN DONATO MILANESE</t>
+          <t>CASTELLO DI ANNONE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>098042</t>
+          <t>034016</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ORIO LITTA</t>
+          <t>FONTEVIVO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>015183</t>
+          <t>005059</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ROBECCHETTO CON INDUNO</t>
+          <t>ISOLA D'ASTI</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>006129</t>
+          <t>033012</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PIETRA MARAZZI</t>
+          <t>CASTELL'ARQUATO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>015130</t>
+          <t>034007</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MAGENTA</t>
+          <t>BUSSETO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I, II</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>033037</t>
+          <t>006051</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PONTENURE</t>
+          <t>CASTELLETTO MONFERRATO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,88 +1619,88 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>005076</t>
+          <t>034027</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MONTEGROSSO D'ASTI</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>II, I</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>006141</t>
+          <t>033041</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>QUARGNENTO</t>
+          <t>SAN PIETRO IN CERRO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>033032</t>
+          <t>006003</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>ALESSANDRIA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>002093</t>
+          <t>005074</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1710,78 +1710,78 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PEZZANA</t>
+          <t>MONTALDO SCARAMPI</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>015248</t>
+          <t>034004</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VILLA CORTESE</t>
+          <t>BERCETO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>015171</t>
+          <t>005071</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>MONGARDINO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>006131</t>
+          <t>006091</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1796,34 +1796,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>POMARO MONFERRATO</t>
+          <t>MASIO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>006122</t>
+          <t>033021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OVIGLIO</t>
+          <t>FIORENZUOLA D'ARDA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,103 +1835,103 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>015134</t>
+          <t>034008</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MARCALLO CON CASONE</t>
+          <t>CALESTANO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>098055</t>
+          <t>033010</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SORDIO</t>
+          <t>CAORSO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>015155</t>
+          <t>033003</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NOSATE</t>
+          <t>BESENZONE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>005050</t>
+          <t>034015</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>COSTIGLIOLE D'ASTI</t>
+          <t>FONTANELLATO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>005048</t>
+          <t>034038</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CORTIGLIONE</t>
+          <t>TERENZO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1970,142 +1970,142 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>098023</t>
+          <t>006142</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CORNOVECCHIO</t>
+          <t>QUATTORDIO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>005034</t>
+          <t>034035</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CELLE ENOMONDO</t>
+          <t>SOLIGNANO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>015071</t>
+          <t>034009</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CERRO AL LAMBRO</t>
+          <t>COLLECCHIO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>003069</t>
+          <t>033039</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GARBAGNA NOVARESE</t>
+          <t>ROTTOFRENO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>006056</t>
+          <t>034045</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CELLA MONTE</t>
+          <t>VARANO DE' MELEGARI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>006011</t>
+          <t>005090</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2115,24 +2115,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BALZOLA</t>
+          <t>REVIGLIASCO D'ASTI</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>034013</t>
+          <t>033011</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FELINO</t>
+          <t>CARPANETO PIACENTINO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>006068</t>
+          <t>005036</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FELIZZANO</t>
+          <t>CERRO TANARO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2186,763 +2186,763 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>006007</t>
+          <t>034012</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ALTAVILLA MONFERRATO</t>
+          <t>CORNIGLIO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>015082</t>
+          <t>005116</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>COLTURANO</t>
+          <t>VIGLIANO D'ASTI</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>015101</t>
+          <t>046020</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DRESANO</t>
+          <t>MOLAZZANA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>015113</t>
+          <t>034026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>INVERUNO</t>
+          <t>PALANZANO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>015097</t>
+          <t>046009</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CUSAGO</t>
+          <t>CASTELNUOVO DI GARFAGNANA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>006073</t>
+          <t>045003</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FRASSINETO PO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>015046</t>
+          <t>046025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CANEGRATE</t>
+          <t>PIEVE FOSCIANA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>015146</t>
+          <t>045005</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>COMANO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>015154</t>
+          <t>045004</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NERVIANO</t>
+          <t>CASOLA IN LUNIGIANA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>018093</t>
+          <t>034022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIRADOLO TERME</t>
+          <t>MONCHIO DELLE CORTI</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>015015</t>
+          <t>046019</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BASIGLIO</t>
+          <t>MINUCCIANO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>098005</t>
+          <t>046008</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BORGO SAN GIOVANNI</t>
+          <t>CAREGGINE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>005022</t>
+          <t>046027</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CASTAGNOLE DELLE LANZE</t>
+          <t>SAN ROMANO IN GARFAGNANA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>098011</t>
+          <t>046031</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CASELLE LANDI</t>
+          <t>VAGLI SOTTO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>015140</t>
+          <t>045011</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>005006</t>
+          <t>046010</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AZZANO D'ASTI</t>
+          <t>CASTIGLIONE DI GARFAGNANA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>015038</t>
+          <t>046006</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BUSCATE</t>
+          <t>CAMPORGIANO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>015005</t>
+          <t>046014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ALBAIRATE</t>
+          <t>FOSCIANDORA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>098029</t>
+          <t>045008</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GUARDAMIGLIO</t>
+          <t>FOSDINOVO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>006023</t>
+          <t>045010</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BOZZOLE</t>
+          <t>MASSA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>006020</t>
+          <t>046023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BORGO SAN MARTINO</t>
+          <t>PIAZZA AL SERCHIO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>018009</t>
+          <t>046035</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BASCAP�</t>
+          <t>VILLA COLLEMANDINA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>015050</t>
+          <t>045007</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CARPIANO</t>
+          <t>FIVIZZANO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>015011</t>
+          <t>035046</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ASSAGO</t>
+          <t>VENTASSO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>005003</t>
+          <t>046037</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ANTIGNANO</t>
+          <t>SILLANO GIUNCUGNANO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>006060</t>
+          <t>009010</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CONIOLO</t>
+          <t>BERGEGGI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>098030</t>
+          <t>004073</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LIVRAGA</t>
+          <t>CORTEMILIA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>015144</t>
+          <t>009042</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>NOLI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>005066</t>
+          <t>004164</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MOMBERCELLI</t>
+          <t>PEZZOLO VALLE UZZONE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>002104</t>
+          <t>005001</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2979,66 +2979,66 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PRAROLO</t>
+          <t>AGLIANO TERME</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>015168</t>
+          <t>006134</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PARABIAGO</t>
+          <t>PONTI</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>034025</t>
+          <t>009004</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NOCETO</t>
+          <t>ALBISOLA SUPERIORE</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3050,169 +3050,169 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>098038</t>
+          <t>009003</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MELETI</t>
+          <t>ALBISSOLA MARINA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>098043</t>
+          <t>005030</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OSPEDALETTO LODIGIANO</t>
+          <t>CASTELNUOVO CALCEA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>018077</t>
+          <t>005021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>INVERNO E MONTELEONE</t>
+          <t>CASSINASCO</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>015125</t>
+          <t>005015</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LOCATE DI TRIULZI</t>
+          <t>CALOSSO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>015164</t>
+          <t>009032</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OSSONA</t>
+          <t>GIUSVALLA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>098037</t>
+          <t>009036</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MASSALENGO</t>
+          <t>MALLARE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>006105</t>
+          <t>005017</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3222,51 +3222,51 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MONTECASTELLO</t>
+          <t>CANELLI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>015002</t>
+          <t>005011</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ABBIATEGRASSO</t>
+          <t>BUBBIO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>005096</t>
+          <t>005060</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ROCCHETTA TANARO</t>
+          <t>LOAZZOLO</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>005058</t>
+          <t>005037</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>INCISA SCAPACCINO</t>
+          <t>CESSOLE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3320,76 +3320,76 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>015024</t>
+          <t>009029</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>BINASCO</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>018079</t>
+          <t>005064</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LANGOSCO</t>
+          <t>MOMBALDONE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>005008</t>
+          <t>009027</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BELVEGLIO</t>
+          <t>DEGO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3401,61 +3401,61 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>033008</t>
+          <t>009048</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CALENDASCO</t>
+          <t>PIANA CRIXIA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>098045</t>
+          <t>005100</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>PIEVE FISSIRAGA</t>
+          <t>SAN MARZANO OLIVETO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>006128</t>
+          <t>004161</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3465,93 +3465,93 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PECETTO DI VALENZA</t>
+          <t>PERLETTO</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>018078</t>
+          <t>006165</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LANDRIANO</t>
+          <t>SPIGNO MONFERRATO</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>018099</t>
+          <t>005104</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>MONTICELLI PAVESE</t>
+          <t>SEROLE</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>033002</t>
+          <t>009044</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ALSENO</t>
+          <t>ORCO FEGLINO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3563,103 +3563,103 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>015007</t>
+          <t>009056</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ARCONATE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>018022</t>
+          <t>009067</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>BREME</t>
+          <t>VEZZI PORTIO</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>033007</t>
+          <t>005113</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CADEO</t>
+          <t>VESIME</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>034014</t>
+          <t>004056</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>FIDENZA</t>
+          <t>CASTIGLIONE TINELLA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3671,22 +3671,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>034017</t>
+          <t>006065</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>FORNOVO DI TARO</t>
+          <t>DENICE</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3698,22 +3698,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>033018</t>
+          <t>009015</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CORTEMAGGIORE</t>
+          <t>CAIRO MONTENOTTE</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3725,115 +3725,115 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>015099</t>
+          <t>005063</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DAIRAGO</t>
+          <t>MOASCA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>098044</t>
+          <t>006093</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OSSAGO LODIGIANO</t>
+          <t>MERANA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>018107</t>
+          <t>004213</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PALESTRO</t>
+          <t>SANTO STEFANO BELBO</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>015173</t>
+          <t>005105</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PIEVE EMANUELE</t>
+          <t>SESSAME</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>005028</t>
+          <t>005098</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>CASTELLO DI ANNONE</t>
+          <t>SAN GIORGIO SCARAMPI</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3860,61 +3860,61 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>015019</t>
+          <t>009005</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>BERNATE TICINO</t>
+          <t>ALTARE</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>098026</t>
+          <t>005094</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>FOMBIO</t>
+          <t>ROCCAVERANO</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>005005</t>
+          <t>005081</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3929,154 +3929,154 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>OLMO GENTILE</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>034016</t>
+          <t>009064</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>FONTEVIVO</t>
+          <t>VADO LIGURE</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>015115</t>
+          <t>009018</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LACCHIARELLA</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>015062</t>
+          <t>005068</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CASTANO PRIMO</t>
+          <t>MONASTERO BORMIDA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>015078</t>
+          <t>009052</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CISLIANO</t>
+          <t>QUILIANO</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>015074</t>
+          <t>009057</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>CESANO BOSCONE</t>
+          <t>SPOTORNO</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>005059</t>
+          <t>005120</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4091,46 +4091,46 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ISOLA D'ASTI</t>
+          <t>VINCHIO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>015118</t>
+          <t>034018</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>LANGHIRANO</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>033012</t>
+          <t>034039</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CASTELL'ARQUATO</t>
+          <t>TIZZANO VAL PARMA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>034007</t>
+          <t>035045</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4167,78 +4167,78 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>BUSSETO</t>
+          <t>VILLA MINOZZO</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>I, II</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>006051</t>
+          <t>036016</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CASTELLETTO MONFERRATO</t>
+          <t>FRASSINORO</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>098008</t>
+          <t>036031</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CASALETTO LODIGIANO</t>
+          <t>PIEVEPELAGO</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>034027</t>
+          <t>036035</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4248,24 +4248,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>RIOLUNATO</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>II, I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>033041</t>
+          <t>036014</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SAN PIETRO IN CERRO</t>
+          <t>FIUMALBO</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4292,22 +4292,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>006003</t>
+          <t>047023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ALESSANDRIA</t>
+          <t>ABETONE CUTIGLIANO</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4319,103 +4319,103 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>005077</t>
+          <t>046011</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>MONTEMAGNO MONFERRATO</t>
+          <t>COREGLIA ANTELMINELLI</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>018087</t>
+          <t>046003</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MARZANO</t>
+          <t>BARGA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>015103</t>
+          <t>046015</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>GAGGIANO</t>
+          <t>GALLICANO</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>005074</t>
+          <t>046036</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>MONTALDO SCARAMPI</t>
+          <t>FABBRICHE DI VERGEMOLI</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4427,22 +4427,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>034004</t>
+          <t>046030</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>STAZZEMA</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4454,211 +4454,211 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>015026</t>
+          <t>046028</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>BOFFALORA SOPRA TICINO</t>
+          <t>SERAVEZZA</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>015010</t>
+          <t>036025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ARLUNO</t>
+          <t>MONTEFIORINO</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>098022</t>
+          <t>036029</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>CORNO GIOVINE</t>
+          <t>PALAGANO</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>003077</t>
+          <t>035041</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>GRANOZZO CON MONTICELLO</t>
+          <t>TOANO</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>098032</t>
+          <t>035042</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LODI VECCHIO</t>
+          <t>VETTO</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>018052</t>
+          <t>035016</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>CONFIENZA</t>
+          <t>CASTELNOVO NE' MONTI</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>005071</t>
+          <t>035011</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>MONGARDINO</t>
+          <t>CARPINETI</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>006091</t>
+          <t>036018</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>MASIO</t>
+          <t>LAMA MOCOGNO</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4670,61 +4670,61 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>006109</t>
+          <t>018038</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>MORANO SUL PO</t>
+          <t>CASTELLETTO DI BRANDUZZO</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>015158</t>
+          <t>006053</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NOVIGLIO</t>
+          <t>CASTELNUOVO SCRIVIA</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>006094</t>
+          <t>006151</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>MIRABELLO MONFERRATO</t>
+          <t>SALE</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4751,49 +4751,49 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>003106</t>
+          <t>018029</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CANNETO PAVESE</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>033021</t>
+          <t>006132</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>FIORENZUOLA D'ARDA</t>
+          <t>PONTECURONE</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>098004</t>
+          <t>018023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4815,24 +4815,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>BORGHETTO LODIGIANO</t>
+          <t>BRESSANA BOTTARONE</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>015041</t>
+          <t>018020</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4842,24 +4842,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>BOSNASCO</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>034008</t>
+          <t>033013</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4869,39 +4869,39 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>CALESTANO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>006047</t>
+          <t>018008</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>CASTELLAZZO BORMIDA</t>
+          <t>BARBIANELLO</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>006026</t>
+          <t>006145</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>CAMAGNA MONFERRATO</t>
+          <t>RIVARONE</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4940,7 +4940,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>098006</t>
+          <t>018115</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4950,51 +4950,51 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>BREMBIO</t>
+          <t>PINAROLO PO</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>006076</t>
+          <t>018161</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>FUBINE</t>
+          <t>TORRICELLA VERZATE</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>006072</t>
+          <t>006174</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5009,88 +5009,88 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>FRASSINELLO MONFERRATO</t>
+          <t>TORTONA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>033010</t>
+          <t>018095</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>CAORSO</t>
+          <t>MONTEBELLO DELLA BATTAGLIA</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>005023</t>
+          <t>018116</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>CASTAGNOLE MONFERRATO</t>
+          <t>PIZZALE</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>033003</t>
+          <t>018120</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>BESENZONE</t>
+          <t>REDAVALLE</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5102,7 +5102,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>015159</t>
+          <t>018124</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5112,105 +5112,105 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>OPERA</t>
+          <t>ROBECCO PAVESE</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>006115</t>
+          <t>018084</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>OCCIMIANO</t>
+          <t>LUNGAVILLA</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>034015</t>
+          <t>018174</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>FONTANELLATO</t>
+          <t>VERRETTO</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>003049</t>
+          <t>033042</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>CERANO</t>
+          <t>SARMATO</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>098015</t>
+          <t>018140</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5220,78 +5220,78 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>CASTIRAGA VIDARDO</t>
+          <t>SANTA GIULETTA</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>002030</t>
+          <t>018153</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>CARESANA</t>
+          <t>STRADELLA</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>015085</t>
+          <t>006181</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CORBETTA</t>
+          <t>VIGUZZOLO</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>015195</t>
+          <t>018033</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5301,24 +5301,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CASEI GEROLA</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>098053</t>
+          <t>018032</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5328,24 +5328,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>SENNA LODIGIANA</t>
+          <t>CASATISMA</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>015189</t>
+          <t>018049</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5355,51 +5355,51 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>CIGOGNOLA</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>006123</t>
+          <t>018057</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>OZZANO MONFERRATO</t>
+          <t>CORVINO SAN QUIRICO</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>018157</t>
+          <t>018182</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5414,46 +5414,46 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>TORRE D'ARESE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>034038</t>
+          <t>006192</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TERENZO</t>
+          <t>ALLUVIONI PIOVERA</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>098056</t>
+          <t>018118</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5463,51 +5463,51 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TAVAZZANO CON VILLAVESCO</t>
+          <t>PORTALBERA</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>006178</t>
+          <t>018187</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VALMACCA</t>
+          <t>ZENEVREDO</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>018150</t>
+          <t>018037</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5522,34 +5522,34 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SIZIANO</t>
+          <t>CASTEGGIO</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>006179</t>
+          <t>018005</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VIGNALE MONFERRATO</t>
+          <t>ARENA PO</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5561,7 +5561,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>018130</t>
+          <t>018024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5576,3493 +5576,10 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ROSASCO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>015201</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>SAN VITTORE OLONA</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>005087</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>PORTACOMARO</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>015184</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>ROBECCO SUL NAVIGLIO</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>098050</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>SANT'ANGELO LODIGIANO</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>015202</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>SAN ZENONE AL LAMBRO</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>015247</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>ZIBIDO SAN GIACOMO</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>006039</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>CASALE MONFERRATO</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>006142</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>QUATTORDIO</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>015191</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>SAN COLOMBANO AL LAMBRO</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>034035</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>SOLIGNANO</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>098059</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>VALERA FRATTA</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>015220</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>TREZZANO SUL NAVIGLIO</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>034009</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>COLLECCHIO</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>015211</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>SETTIMO MILANESE</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>015036</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>BUCCINASCO</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>015012</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>BAREGGIO</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>033039</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>ROTTOFRENO</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>018123</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>ROBBIO</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>003149</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>TRECATE</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>018180</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>VILLANTERIO</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>006154</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>SAN SALVATORE MONFERRATO</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>003131</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>ROMENTINO</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>034045</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>VARANO DE' MELEGARI</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>005090</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>REVIGLIASCO D'ASTI</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>018176</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>VIDIGULFO</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>018048</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>CHIGNOLO PO</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>098021</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>CORNEGLIANO LAUDENSE</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>015087</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>CORNAREDO</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>015093</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>CORSICO</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>015061</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>CASSINETTA DI LUGAGNANO</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>033011</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>CARPANETO PIACENTINO</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>098028</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>LO</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>GRAFFIGNANA</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>018027</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>CANDIA LOMELLINA</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>005036</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>CERRO TANARO</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>034012</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>CORNIGLIO</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>015096</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>CUGGIONO</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>006193</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>LU E CUCCARO MONFERRATO</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>003144</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>TERDOBBIATE</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>006171</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>TERRUGGIA</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>015243</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>VITTUONE</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>015200</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>SANTO STEFANO TICINO</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>006173</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>TICINETO</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>005116</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>VIGLIANO D'ASTI</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>015194</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>SAN GIORGIO SU LEGNANO</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>015244</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>VIZZOLO PREDABISSI</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>002082</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>VC</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>MOTTA DE' CONTI</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>LIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>046020</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>MOLAZZANA</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>034026</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>PALANZANO</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>046009</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>CASTELNUOVO DI GARFAGNANA</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>045003</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>CARRARA</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>046025</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>PIEVE FOSCIANA</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>045005</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>COMANO</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>045004</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>CASOLA IN LUNIGIANA</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>034022</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>MONCHIO DELLE CORTI</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>046019</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>MINUCCIANO</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>046008</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>CAREGGINE</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>046027</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>SAN ROMANO IN GARFAGNANA</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>046031</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>VAGLI SOTTO</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>045011</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>MONTIGNOSO</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>046010</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>CASTIGLIONE DI GARFAGNANA</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>046006</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>CAMPORGIANO</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>046014</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>FOSCIANDORA</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>045008</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>FOSDINOVO</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>045010</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>MASSA</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>046023</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>PIAZZA AL SERCHIO</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>046035</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>VILLA COLLEMANDINA</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>045007</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>FIVIZZANO</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>035046</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>VENTASSO</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>046037</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>SILLANO GIUNCUGNANO</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>009010</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>BERGEGGI</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>004073</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>CORTEMILIA</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>009042</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>NOLI</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>004164</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>PEZZOLO VALLE UZZONE</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>005001</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>AGLIANO TERME</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>006134</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>PONTI</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>009004</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>ALBISOLA SUPERIORE</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>009003</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>ALBISSOLA MARINA</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>005030</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>CASTELNUOVO CALCEA</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>005021</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>CASSINASCO</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>005015</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>CALOSSO</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>009032</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>GIUSVALLA</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>009036</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>MALLARE</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>005017</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>CANELLI</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>005011</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>BUBBIO</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>005060</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>LOAZZOLO</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>005037</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>CESSOLE</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>009029</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>FINALE LIGURE</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>005064</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>MOMBALDONE</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>009027</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>DEGO</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>009048</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>PIANA CRIXIA</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>005100</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>SAN MARZANO OLIVETO</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>004161</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>PERLETTO</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>006165</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>SPIGNO MONFERRATO</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>005104</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>SEROLE</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>009044</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>ORCO FEGLINO</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>009056</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>SAVONA</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>009067</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>VEZZI PORTIO</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>005113</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>VESIME</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>004056</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>CASTIGLIONE TINELLA</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>006065</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>DENICE</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>009015</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>CAIRO MONTENOTTE</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>005063</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>MOASCA</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>006093</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>MERANA</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>004213</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>SANTO STEFANO BELBO</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>005105</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>SESSAME</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>005098</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>SAN GIORGIO SCARAMPI</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>009005</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>ALTARE</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>005094</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>ROCCAVERANO</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>005081</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>OLMO GENTILE</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>009064</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>VADO LIGURE</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>009018</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>CARCARE</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>005068</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>MONASTERO BORMIDA</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>009052</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>QUILIANO</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>009057</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>LIGURIA</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>SPOTORNO</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>005120</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>PIEMONTE</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>VINCHIO</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>034018</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>LANGHIRANO</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>034039</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>TIZZANO VAL PARMA</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>035045</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>VILLA MINOZZO</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>036016</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>FRASSINORO</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>036031</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>PIEVEPELAGO</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>036035</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>RIOLUNATO</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>036014</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>EMILIA ROMAGNA</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>FIUMALBO</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>047023</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>ABETONE CUTIGLIANO</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>046011</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>COREGLIA ANTELMINELLI</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>046003</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>BARGA</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>046015</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>GALLICANO</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>046036</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>FABBRICHE DI VERGEMOLI</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>046030</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>STAZZEMA</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>046028</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>TOSCANA</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>SERAVEZZA</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
         <is>
           <t>II</t>
         </is>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>II, III</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>II, III</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034031</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MEDESANO</t>
+          <t>SALA BAGANZA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -512,61 +512,61 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>005089</t>
+          <t>034036</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>REFRANCORE</t>
+          <t>SORAGNA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>034031</t>
+          <t>006163</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SALA BAGANZA</t>
+          <t>SOLERO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>034036</t>
+          <t>033035</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,24 +576,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SORAGNA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006163</t>
+          <t>006129</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SOLERO</t>
+          <t>PIETRA MARAZZI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,7 +620,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>033040</t>
+          <t>033037</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN GIORGIO PIACENTINO</t>
+          <t>PONTENURE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,34 +647,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>098049</t>
+          <t>005076</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN ROCCO AL PORTO</t>
+          <t>MONTEGROSSO D'ASTI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>033035</t>
+          <t>033032</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -689,19 +689,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>005099</t>
+          <t>006122</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -711,24 +711,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN MARTINO ALFIERI</t>
+          <t>OVIGLIO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>006129</t>
+          <t>005050</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PIETRA MARAZZI</t>
+          <t>COSTIGLIOLE D'ASTI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,61 +755,61 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>033037</t>
+          <t>005048</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PONTENURE</t>
+          <t>CORTIGLIONE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>005076</t>
+          <t>034013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MONTEGROSSO D'ASTI</t>
+          <t>FELINO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>006141</t>
+          <t>006068</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -824,34 +824,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>QUARGNENTO</t>
+          <t>FELIZZANO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>033032</t>
+          <t>005022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>CASTAGNOLE DELLE LANZE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>006122</t>
+          <t>005066</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OVIGLIO</t>
+          <t>MOMBERCELLI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,34 +890,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>005050</t>
+          <t>034025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COSTIGLIOLE D'ASTI</t>
+          <t>NOCETO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>005048</t>
+          <t>006105</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -927,24 +927,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CORTIGLIONE</t>
+          <t>MONTECASTELLO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LIM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>005034</t>
+          <t>005096</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -959,46 +959,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CELLE ENOMONDO</t>
+          <t>ROCCHETTA TANARO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>034013</t>
+          <t>005058</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FELINO</t>
+          <t>INCISA SCAPACCINO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>006068</t>
+          <t>005008</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FELIZZANO</t>
+          <t>BELVEGLIO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>005022</t>
+          <t>033008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CASTAGNOLE DELLE LANZE</t>
+          <t>CALENDASCO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,169 +1052,169 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>098011</t>
+          <t>033002</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CASELLE LANDI</t>
+          <t>ALSENO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>005006</t>
+          <t>033007</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AZZANO D'ASTI</t>
+          <t>CADEO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>005003</t>
+          <t>034014</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ANTIGNANO</t>
+          <t>FIDENZA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>005066</t>
+          <t>033018</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MOMBERCELLI</t>
+          <t>CORTEMAGGIORE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>034025</t>
+          <t>005028</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NOCETO</t>
+          <t>CASTELLO DI ANNONE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>006105</t>
+          <t>034016</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MONTECASTELLO</t>
+          <t>FONTEVIVO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>005096</t>
+          <t>005059</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ROCCHETTA TANARO</t>
+          <t>ISOLA D'ASTI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,61 +1241,61 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>005058</t>
+          <t>034007</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>INCISA SCAPACCINO</t>
+          <t>BUSSETO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I, II</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>005008</t>
+          <t>034027</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BELVEGLIO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II, I</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>033008</t>
+          <t>033041</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1310,100 +1310,100 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CALENDASCO</t>
+          <t>SAN PIETRO IN CERRO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>033002</t>
+          <t>006003</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ALSENO</t>
+          <t>ALESSANDRIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>033007</t>
+          <t>005074</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CADEO</t>
+          <t>MONTALDO SCARAMPI</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>034014</t>
+          <t>006091</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FIDENZA</t>
+          <t>MASIO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>034017</t>
+          <t>033021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FORNOVO DI TARO</t>
+          <t>FIORENZUOLA D'ARDA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,7 +1430,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>033018</t>
+          <t>033010</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1445,46 +1445,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CORTEMAGGIORE</t>
+          <t>CAORSO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>005028</t>
+          <t>033003</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CASTELLO DI ANNONE</t>
+          <t>BESENZONE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>034016</t>
+          <t>034015</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FONTEVIVO</t>
+          <t>FONTANELLATO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>005059</t>
+          <t>006142</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ISOLA D'ASTI</t>
+          <t>QUATTORDIO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>033012</t>
+          <t>034009</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CASTELL'ARQUATO</t>
+          <t>COLLECCHIO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>034007</t>
+          <t>033039</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1575,24 +1575,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BUSSETO</t>
+          <t>ROTTOFRENO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I, II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>006051</t>
+          <t>005036</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1602,66 +1602,66 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CASTELLETTO MONFERRATO</t>
+          <t>CERRO TANARO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>034027</t>
+          <t>005116</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>VIGLIANO D'ASTI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>II, I</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>033041</t>
+          <t>046020</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAN PIETRO IN CERRO</t>
+          <t>MOLAZZANA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,76 +1673,76 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>006003</t>
+          <t>034026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ALESSANDRIA</t>
+          <t>PALANZANO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>005074</t>
+          <t>046009</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MONTALDO SCARAMPI</t>
+          <t>CASTELNUOVO DI GARFAGNANA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>034004</t>
+          <t>045003</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,76 +1754,76 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>005071</t>
+          <t>046008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MONGARDINO</t>
+          <t>CAREGGINE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>006091</t>
+          <t>046031</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MASIO</t>
+          <t>VAGLI SOTTO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>033021</t>
+          <t>045011</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FIORENZUOLA D'ARDA</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>034008</t>
+          <t>046014</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CALESTANO</t>
+          <t>FOSCIANDORA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,34 +1862,34 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>033010</t>
+          <t>045010</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CAORSO</t>
+          <t>MASSA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>033003</t>
+          <t>035046</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1899,66 +1899,66 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BESENZONE</t>
+          <t>VENTASSO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>II, III</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>034015</t>
+          <t>004073</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FONTANELLATO</t>
+          <t>CORTEMILIA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>034038</t>
+          <t>004164</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TERENZO</t>
+          <t>PEZZOLO VALLE UZZONE</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1970,7 +1970,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>006142</t>
+          <t>005001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>QUATTORDIO</t>
+          <t>AGLIANO TERME</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1997,22 +1997,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>034035</t>
+          <t>009004</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SOLIGNANO</t>
+          <t>ALBISOLA SUPERIORE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2024,22 +2024,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>034009</t>
+          <t>009003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>COLLECCHIO</t>
+          <t>ALBISSOLA MARINA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2051,22 +2051,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>033039</t>
+          <t>005030</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ROTTOFRENO</t>
+          <t>CASTELNUOVO CALCEA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2078,34 +2078,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>034045</t>
+          <t>005021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VARANO DE' MELEGARI</t>
+          <t>CASSINASCO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>005090</t>
+          <t>005015</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2120,34 +2120,34 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>REVIGLIASCO D'ASTI</t>
+          <t>CALOSSO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>033011</t>
+          <t>009032</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CARPANETO PIACENTINO</t>
+          <t>GIUSVALLA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>005036</t>
+          <t>005017</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2174,46 +2174,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CERRO TANARO</t>
+          <t>CANELLI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>034012</t>
+          <t>005011</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CORNIGLIO</t>
+          <t>BUBBIO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>005116</t>
+          <t>005060</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2228,61 +2228,61 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VIGLIANO D'ASTI</t>
+          <t>LOAZZOLO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>046020</t>
+          <t>005037</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MOLAZZANA</t>
+          <t>CESSOLE</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>034026</t>
+          <t>009027</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PALANZANO</t>
+          <t>DEGO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2294,22 +2294,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>046009</t>
+          <t>009048</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CASTELNUOVO DI GARFAGNANA</t>
+          <t>PIANA CRIXIA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2321,22 +2321,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>045003</t>
+          <t>005100</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>SAN MARZANO OLIVETO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2348,76 +2348,76 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>046025</t>
+          <t>004161</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PIEVE FOSCIANA</t>
+          <t>PERLETTO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>045005</t>
+          <t>009056</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>COMANO</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>045004</t>
+          <t>005113</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CASOLA IN LUNIGIANA</t>
+          <t>VESIME</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2429,49 +2429,49 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>034022</t>
+          <t>004056</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MONCHIO DELLE CORTI</t>
+          <t>CASTIGLIONE TINELLA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>II, III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>046019</t>
+          <t>009015</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MINUCCIANO</t>
+          <t>CAIRO MONTENOTTE</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2483,22 +2483,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>046008</t>
+          <t>005063</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CAREGGINE</t>
+          <t>MOASCA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2510,22 +2510,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>046027</t>
+          <t>004213</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAN ROMANO IN GARFAGNANA</t>
+          <t>SANTO STEFANO BELBO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2537,76 +2537,76 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>046031</t>
+          <t>005105</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VAGLI SOTTO</t>
+          <t>SESSAME</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>045011</t>
+          <t>005098</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MONTIGNOSO</t>
+          <t>SAN GIORGIO SCARAMPI</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>046010</t>
+          <t>009005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CASTIGLIONE DI GARFAGNANA</t>
+          <t>ALTARE</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2618,22 +2618,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>046006</t>
+          <t>009018</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CAMPORGIANO</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2645,76 +2645,76 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>046014</t>
+          <t>005068</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>FOSCIANDORA</t>
+          <t>MONASTERO BORMIDA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>045008</t>
+          <t>005120</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FOSDINOVO</t>
+          <t>VINCHIO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>045010</t>
+          <t>034018</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MASSA</t>
+          <t>LANGHIRANO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2726,22 +2726,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>046023</t>
+          <t>034039</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PIAZZA AL SERCHIO</t>
+          <t>TIZZANO VAL PARMA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2753,22 +2753,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>046035</t>
+          <t>035045</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VILLA COLLEMANDINA</t>
+          <t>VILLA MINOZZO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2780,34 +2780,34 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>045007</t>
+          <t>036016</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FIVIZZANO</t>
+          <t>FRASSINORO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>035046</t>
+          <t>036031</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2817,39 +2817,39 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VENTASSO</t>
+          <t>PIEVEPELAGO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>II, III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>046037</t>
+          <t>036035</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SILLANO GIUNCUGNANO</t>
+          <t>RIOLUNATO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2861,22 +2861,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>009010</t>
+          <t>036014</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BERGEGGI</t>
+          <t>FIUMALBO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2888,22 +2888,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>004073</t>
+          <t>047023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CORTEMILIA</t>
+          <t>ABETONE CUTIGLIANO</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2915,22 +2915,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>009042</t>
+          <t>046011</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NOLI</t>
+          <t>COREGLIA ANTELMINELLI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2942,22 +2942,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>004164</t>
+          <t>046003</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PEZZOLO VALLE UZZONE</t>
+          <t>BARGA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2969,76 +2969,76 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>005001</t>
+          <t>046015</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AGLIANO TERME</t>
+          <t>GALLICANO</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>006134</t>
+          <t>046036</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PONTI</t>
+          <t>FABBRICHE DI VERGEMOLI</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>009004</t>
+          <t>046030</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ALBISOLA SUPERIORE</t>
+          <t>STAZZEMA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3050,22 +3050,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>009003</t>
+          <t>046028</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ALBISSOLA MARINA</t>
+          <t>SERAVEZZA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3077,76 +3077,76 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>005030</t>
+          <t>036025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CASTELNUOVO CALCEA</t>
+          <t>MONTEFIORINO</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>005021</t>
+          <t>036029</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CASSINASCO</t>
+          <t>PALAGANO</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>005015</t>
+          <t>035041</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CALOSSO</t>
+          <t>TOANO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3158,22 +3158,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>009032</t>
+          <t>035042</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>GIUSVALLA</t>
+          <t>VETTO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3185,49 +3185,49 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>009036</t>
+          <t>035016</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MALLARE</t>
+          <t>CASTELNOVO NE' MONTI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>005017</t>
+          <t>035011</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CANELLI</t>
+          <t>CARPINETI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3239,61 +3239,61 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>005011</t>
+          <t>036018</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>BUBBIO</t>
+          <t>LAMA MOCOGNO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>005060</t>
+          <t>018038</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LOAZZOLO</t>
+          <t>CASTELLETTO DI BRANDUZZO</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>005037</t>
+          <t>006053</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3303,93 +3303,93 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CESSOLE</t>
+          <t>CASTELNUOVO SCRIVIA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>009029</t>
+          <t>006151</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>SALE</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>005064</t>
+          <t>018029</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MOMBALDONE</t>
+          <t>CANNETO PAVESE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>009027</t>
+          <t>006132</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DEGO</t>
+          <t>PONTECURONE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3401,22 +3401,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>009048</t>
+          <t>018023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PIANA CRIXIA</t>
+          <t>BRESSANA BOTTARONE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3428,130 +3428,130 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>005100</t>
+          <t>018020</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SAN MARZANO OLIVETO</t>
+          <t>BOSNASCO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>004161</t>
+          <t>033013</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PERLETTO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>006165</t>
+          <t>018008</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SPIGNO MONFERRATO</t>
+          <t>BARBIANELLO</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>005104</t>
+          <t>018115</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SEROLE</t>
+          <t>PINAROLO PO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>009044</t>
+          <t>018161</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ORCO FEGLINO</t>
+          <t>TORRICELLA VERZATE</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3563,49 +3563,49 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>009056</t>
+          <t>006174</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>TORTONA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>009067</t>
+          <t>018095</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VEZZI PORTIO</t>
+          <t>MONTEBELLO DELLA BATTAGLIA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3617,49 +3617,49 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>005113</t>
+          <t>018116</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VESIME</t>
+          <t>PIZZALE</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>004056</t>
+          <t>018120</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CASTIGLIONE TINELLA</t>
+          <t>REDAVALLE</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3671,49 +3671,49 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>006065</t>
+          <t>018124</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DENICE</t>
+          <t>ROBECCO PAVESE</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>009015</t>
+          <t>018084</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CAIRO MONTENOTTE</t>
+          <t>LUNGAVILLA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3725,22 +3725,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>005063</t>
+          <t>018174</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MOASCA</t>
+          <t>VERRETTO</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3752,49 +3752,49 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>006093</t>
+          <t>033042</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>MERANA</t>
+          <t>SARMATO</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>004213</t>
+          <t>018140</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SANTO STEFANO BELBO</t>
+          <t>SANTA GIULETTA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3806,34 +3806,34 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>005105</t>
+          <t>018153</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SESSAME</t>
+          <t>STRADELLA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>005098</t>
+          <t>006181</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3843,120 +3843,120 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SAN GIORGIO SCARAMPI</t>
+          <t>VIGUZZOLO</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>009005</t>
+          <t>018033</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ALTARE</t>
+          <t>CASEI GEROLA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>005094</t>
+          <t>018032</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ROCCAVERANO</t>
+          <t>CASATISMA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>005081</t>
+          <t>018049</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>OLMO GENTILE</t>
+          <t>CIGOGNOLA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>009064</t>
+          <t>018057</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VADO LIGURE</t>
+          <t>CORVINO SAN QUIRICO</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3968,22 +3968,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>009018</t>
+          <t>018182</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3995,76 +3995,76 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>005068</t>
+          <t>018118</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>MONASTERO BORMIDA</t>
+          <t>PORTALBERA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>009052</t>
+          <t>018187</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>QUILIANO</t>
+          <t>ZENEVREDO</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>009057</t>
+          <t>018037</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LIGURIA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SPOTORNO</t>
+          <t>CASTEGGIO</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4076,22 +4076,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>005120</t>
+          <t>018005</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VINCHIO</t>
+          <t>ARENA PO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4103,22 +4103,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>034018</t>
+          <t>018024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LOMBARDIA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LANGHIRANO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4130,22 +4130,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>034039</t>
+          <t>004020</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>TIZZANO VAL PARMA</t>
+          <t>BENEVELLO</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4157,22 +4157,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>035045</t>
+          <t>004004</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VILLA MINOZZO</t>
+          <t>ALBARETTO DELLA TORRE</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>036016</t>
+          <t>004141</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>FRASSINORO</t>
+          <t>MONTEZEMOLO</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4211,22 +4211,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>036031</t>
+          <t>004097</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PIEVEPELAGO</t>
+          <t>GORZEGNO</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4238,7 +4238,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>036035</t>
+          <t>034024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>RIOLUNATO</t>
+          <t>NEVIANO DEGLI ARDUINI</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4265,22 +4265,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>036014</t>
+          <t>009022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>FIUMALBO</t>
+          <t>CELLE LIGURE</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>047023</t>
+          <t>047007</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ABETONE CUTIGLIANO</t>
+          <t>MARLIANA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4319,22 +4319,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>046011</t>
+          <t>004024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>COREGLIA ANTELMINELLI</t>
+          <t>BORGOMALE</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4346,7 +4346,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>046003</t>
+          <t>046004</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>BARGA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4373,22 +4373,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>046015</t>
+          <t>004175</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>GALLICANO</t>
+          <t>PRIERO</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4400,7 +4400,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>046036</t>
+          <t>047014</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4410,39 +4410,39 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>FABBRICHE DI VERGEMOLI</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>046030</t>
+          <t>009047</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>STAZZEMA</t>
+          <t>PALLARE</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4454,22 +4454,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>046028</t>
+          <t>004074</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TOSCANA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SERAVEZZA</t>
+          <t>COSSANO BELBO</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4481,7 +4481,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>036025</t>
+          <t>036011</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4496,34 +4496,34 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MONTEFIORINO</t>
+          <t>FANANO</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III, II</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>036029</t>
+          <t>004035</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PALAGANO</t>
+          <t>CAMERANA</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4535,22 +4535,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>035041</t>
+          <t>004054</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>TOANO</t>
+          <t>CASTELNUOVO DI CEVA</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4562,22 +4562,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>035042</t>
+          <t>004098</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VETTO</t>
+          <t>GOTTASECCA</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4589,22 +4589,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>035016</t>
+          <t>004076</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>CASTELNOVO NE' MONTI</t>
+          <t>CRAVANZANA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4616,22 +4616,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>035011</t>
+          <t>004021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>CARPINETI</t>
+          <t>BERGOLO</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4643,22 +4643,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>036018</t>
+          <t>004199</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LAMA MOCOGNO</t>
+          <t>SALE DELLE LANGHE</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4670,22 +4670,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>018038</t>
+          <t>004200</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>CASTELLETTO DI BRANDUZZO</t>
+          <t>SALE SAN GIOVANNI</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4697,7 +4697,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>006053</t>
+          <t>004131</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4707,66 +4707,66 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>CASTELNUOVO SCRIVIA</t>
+          <t>MONESIGLIO</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>006151</t>
+          <t>047012</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>SALE</t>
+          <t>PESCIA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>018029</t>
+          <t>004220</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>CANNETO PAVESE</t>
+          <t>SINIO</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4778,7 +4778,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>006132</t>
+          <t>004178</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PONTECURONE</t>
+          <t>PRUNETTO</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,22 +4805,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>018023</t>
+          <t>004050</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>BRESSANA BOTTARONE</t>
+          <t>CASTELLETTO UZZONE</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4832,76 +4832,76 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>018020</t>
+          <t>004201</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>BOSNASCO</t>
+          <t>SALICETO</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>033013</t>
+          <t>004195</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>RODDINO</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>018008</t>
+          <t>004109</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>BARBIANELLO</t>
+          <t>LEVICE</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4913,49 +4913,49 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>006145</t>
+          <t>037033</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>RIVARONE</t>
+          <t>LIZZANO IN BELVEDERE</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>018115</t>
+          <t>009026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>PINAROLO PO</t>
+          <t>COSSERIA</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4967,34 +4967,34 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>018161</t>
+          <t>046002</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TORRICELLA VERZATE</t>
+          <t>BAGNI DI LUCCA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>006174</t>
+          <t>004106</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5004,39 +5004,39 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>TORTONA</t>
+          <t>LEQUIO BERRIA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>018095</t>
+          <t>009051</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>MONTEBELLO DELLA BATTAGLIA</t>
+          <t>PONTINVREA</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5048,49 +5048,49 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>018116</t>
+          <t>033024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>PIZZALE</t>
+          <t>GRAGNANO TREBBIENSE</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>018120</t>
+          <t>004063</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>REDAVALLE</t>
+          <t>CERRETO LANGHE</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5102,49 +5102,49 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>018124</t>
+          <t>037062</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ROBECCO PAVESE</t>
+          <t>ALTO RENO TERME</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>018084</t>
+          <t>004219</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LUNGAVILLA</t>
+          <t>SERRAVALLE LANGHE</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5156,76 +5156,76 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>018174</t>
+          <t>047024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VERRETTO</t>
+          <t>SAN MARCELLO PITEGLIO</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>033042</t>
+          <t>004027</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EMILIA ROMAGNA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>SARMATO</t>
+          <t>BOSSOLASCO</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>018140</t>
+          <t>004007</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SANTA GIULETTA</t>
+          <t>ARGUELLO</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5237,49 +5237,49 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>018153</t>
+          <t>004026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>STRADELLA</t>
+          <t>BOSIA</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>006181</t>
+          <t>034019</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>EMILIA ROMAGNA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VIGUZZOLO</t>
+          <t>LESIGNANO DE' BAGNI</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5291,49 +5291,49 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>018033</t>
+          <t>046034</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CASEI GEROLA</t>
+          <t>VILLA BASILICA</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>018032</t>
+          <t>009050</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>CASATISMA</t>
+          <t>PLODIO</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5345,22 +5345,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>018049</t>
+          <t>004150</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>CIGOGNOLA</t>
+          <t>NIELLA BELBO</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5372,22 +5372,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>018057</t>
+          <t>009054</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>CORVINO SAN QUIRICO</t>
+          <t>ROCCAVIGNALE</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5399,22 +5399,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>018182</t>
+          <t>004193</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>ROCCHETTA BELBO</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5426,103 +5426,103 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>006192</t>
+          <t>047018</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PIEMONTE</t>
+          <t>TOSCANA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ALLUVIONI PIOVERA</t>
+          <t>SAMBUCA PISTOIESE</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>018118</t>
+          <t>004196</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PORTALBERA</t>
+          <t>RODELLO</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>018187</t>
+          <t>004057</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ZENEVREDO</t>
+          <t>CASTINO</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>018037</t>
+          <t>004137</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>PIEMONTE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>CASTEGGIO</t>
+          <t>MONTELUPO ALBESE</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5534,54 +5534,270 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>018005</t>
+          <t>009038</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ARENA PO</t>
+          <t>MILLESIMO</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>018024</t>
+          <t>009023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LOMBARDIA</t>
+          <t>LIGURIA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>CENGIO</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>II</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>009065</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>LIGURIA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>VARAZZE</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>009058</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>LIGURIA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>STELLA</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>004070</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PIEMONTE</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CISSONE</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>004088</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PIEMONTE</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>FEISOGLIO</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>034042</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EMILIA ROMAGNA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>TRAVERSETOLO</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>004226</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PIEMONTE</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>TORRE BORMIDA</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>033023</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>EMILIA ROMAGNA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>GOSSOLENGO</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>046022</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>TOSCANA</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>PESCAGLIA</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>

--- a/Download/ZoneCEV/ZCEV.xlsx
+++ b/Download/ZoneCEV/ZCEV.xlsx
@@ -5797,7 +5797,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
     </row>
